--- a/tams-invest-parent/tams-invest-portfolio/src/main/resources/tpl/ActualTimeAsset001.xlsx
+++ b/tams-invest-parent/tams-invest-portfolio/src/main/resources/tpl/ActualTimeAsset001.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="23628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BS\tams\tams-invest-parent\tams-invest-portfolio\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\guilin\tams-invest-parent\tams-invest-portfolio\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84FCADCE-B69F-4429-A22B-92FE27829CD1}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="930" yWindow="360" windowWidth="19935" windowHeight="7770"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,14 +20,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>组合名称</t>
   </si>
   <si>
-    <t>证券账户/通道代码</t>
-  </si>
-  <si>
     <t>资产类型</t>
   </si>
   <si>
@@ -48,21 +46,22 @@
     <t>交易可用持仓</t>
   </si>
   <si>
-    <t>预减持仓</t>
-  </si>
-  <si>
     <t>质押持仓</t>
   </si>
   <si>
     <t>市值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>证券账户</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -73,6 +72,14 @@
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -97,8 +104,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -117,7 +125,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -159,7 +167,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -192,9 +200,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -227,6 +252,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -402,58 +444,55 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="17" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="8" max="8" width="12.5" customWidth="1"/>
-    <col min="9" max="9" width="12.375" customWidth="1"/>
-    <col min="11" max="11" width="11.375" customWidth="1"/>
+    <col min="8" max="8" width="12.44140625" customWidth="1"/>
+    <col min="9" max="9" width="12.33203125" customWidth="1"/>
+    <col min="10" max="10" width="11.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>